--- a/app/src/main/assets/templates/elevator_monthly_stat.xlsx
+++ b/app/src/main/assets/templates/elevator_monthly_stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="12935" activeTab="1"/>
+    <workbookView windowWidth="30720" windowHeight="12935"/>
   </bookViews>
   <sheets>
     <sheet name="办公楼统计表" sheetId="113" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">办公楼统计表!$A$1:$L$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'商场统计表 '!$A$1:$L$27</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <customWorkbookViews>
     <customWorkbookView name="kymtang - 个人视图" guid="{B9BA8337-1B7F-4DB2-BC23-2E5B288FACA4}" personalView="1" maximized="1" windowWidth="1276" windowHeight="781" activeSheetId="0"/>
   </customWorkbookViews>
@@ -38,11 +38,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
   <si>
     <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>天荟云洲电梯</t>
     </r>
     <r>
@@ -133,11 +128,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">        </t>
     </r>
     <r>
@@ -199,11 +189,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>天荟广场电梯</t>
     </r>
     <r>
@@ -237,7 +222,7 @@
     <numFmt numFmtId="177" formatCode="h:mm;@"/>
     <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="36">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -289,6 +274,11 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -443,6 +433,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Helv"/>
       <charset val="134"/>
@@ -450,6 +452,11 @@
     <font>
       <sz val="18"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -903,210 +910,210 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1166,13 +1173,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="71" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="71" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="71" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="71" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="71" applyFont="1"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="71" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="71" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="71" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="71" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="71" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="71" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="71" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="71" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="71" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="71" applyFont="1"/>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="3" xfId="71" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="71" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1181,15 +1195,19 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="71" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="71" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="71" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="71" applyFont="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="8" xfId="71" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="71" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="71" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="71" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="71" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="71" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="71" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="71" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="71"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="71" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="79">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2358,267 +2376,267 @@
       <c r="L9" s="22"/>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="18"/>
       <c r="I10" s="19"/>
       <c r="J10" s="20"/>
       <c r="K10" s="21"/>
-      <c r="L10" s="22"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="H11" s="18"/>
       <c r="I11" s="19"/>
       <c r="J11" s="20"/>
       <c r="K11" s="21"/>
-      <c r="L11" s="22"/>
-      <c r="N11" s="23"/>
+      <c r="L11" s="25"/>
+      <c r="N11" s="26"/>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
       <c r="H12" s="18"/>
       <c r="I12" s="19"/>
       <c r="J12" s="20"/>
       <c r="K12" s="21"/>
-      <c r="L12" s="22"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="16"/>
       <c r="G13" s="17"/>
       <c r="H13" s="18"/>
       <c r="I13" s="19"/>
       <c r="J13" s="20"/>
       <c r="K13" s="21"/>
-      <c r="L13" s="22"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="H14" s="18"/>
       <c r="I14" s="19"/>
       <c r="J14" s="20"/>
       <c r="K14" s="21"/>
-      <c r="L14" s="22"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
       <c r="H15" s="18"/>
       <c r="I15" s="19"/>
       <c r="J15" s="20"/>
       <c r="K15" s="21"/>
-      <c r="L15" s="22"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="16"/>
       <c r="G16" s="17"/>
       <c r="H16" s="18"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
       <c r="K16" s="21"/>
-      <c r="L16" s="22"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="16"/>
       <c r="G17" s="17"/>
       <c r="H17" s="18"/>
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
       <c r="K17" s="21"/>
-      <c r="L17" s="22"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="25" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="28" t="s">
+      <c r="F18" s="34"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="27" t="s">
+      <c r="I18" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="30">
+      <c r="J18" s="37">
         <f>G18/14</f>
         <v>0</v>
       </c>
-      <c r="K18" s="31" t="s">
+      <c r="K18" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="L18" s="32"/>
+      <c r="L18" s="39"/>
     </row>
     <row r="19" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A19" s="33"/>
-      <c r="B19" s="25" t="s">
+      <c r="A19" s="40"/>
+      <c r="B19" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="25" t="s">
+      <c r="C19" s="41"/>
+      <c r="D19" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="28" t="s">
+      <c r="I19" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="35"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="42"/>
     </row>
     <row r="20" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A20" s="33"/>
-      <c r="B20" s="25" t="s">
+      <c r="A20" s="40"/>
+      <c r="B20" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="25" t="s">
+      <c r="C20" s="41"/>
+      <c r="D20" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="28" t="s">
+      <c r="F20" s="34"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="I20" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="36">
+      <c r="J20" s="44">
         <f>G20/2</f>
         <v>0</v>
       </c>
-      <c r="K20" s="37" t="s">
+      <c r="K20" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="35"/>
+      <c r="L20" s="42"/>
     </row>
     <row r="21" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A21" s="33"/>
-      <c r="B21" s="25" t="s">
+      <c r="A21" s="40"/>
+      <c r="B21" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="I21" s="28" t="s">
+      <c r="C21" s="41"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="I21" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="35"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="42"/>
     </row>
     <row r="22" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A22" s="38"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="41"/>
+      <c r="A22" s="46"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="51"/>
     </row>
     <row r="23" ht="3.75" customHeight="1" spans="1:12">
-      <c r="A23" s="42"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
     </row>
     <row r="24" ht="27" customHeight="1" spans="1:12">
       <c r="A24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
       <c r="G24" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="42"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
     </row>
     <row r="25" ht="6.75" customHeight="1" spans="1:12">
       <c r="A25" s="6"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="42"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
     </row>
     <row r="26" ht="17.25" customHeight="1" spans="1:12">
       <c r="A26" s="5" t="s">
@@ -2633,36 +2651,36 @@
         <v>27</v>
       </c>
       <c r="H26" s="5"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
     </row>
     <row r="27" ht="9.75" customHeight="1" spans="1:12">
-      <c r="A27" s="42"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="42"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="52"/>
     </row>
     <row r="29" ht="19.35" customHeight="1"/>
   </sheetData>
@@ -2866,267 +2884,267 @@
       <c r="L9" s="22"/>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="18"/>
       <c r="I10" s="19"/>
       <c r="J10" s="20"/>
       <c r="K10" s="21"/>
-      <c r="L10" s="22"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="H11" s="18"/>
       <c r="I11" s="19"/>
       <c r="J11" s="20"/>
       <c r="K11" s="21"/>
-      <c r="L11" s="22"/>
-      <c r="N11" s="23"/>
+      <c r="L11" s="25"/>
+      <c r="N11" s="26"/>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
       <c r="H12" s="18"/>
       <c r="I12" s="19"/>
       <c r="J12" s="20"/>
       <c r="K12" s="21"/>
-      <c r="L12" s="22"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="16"/>
       <c r="G13" s="17"/>
       <c r="H13" s="18"/>
       <c r="I13" s="19"/>
       <c r="J13" s="20"/>
       <c r="K13" s="21"/>
-      <c r="L13" s="22"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="H14" s="18"/>
       <c r="I14" s="19"/>
       <c r="J14" s="20"/>
       <c r="K14" s="21"/>
-      <c r="L14" s="22"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
       <c r="H15" s="18"/>
       <c r="I15" s="19"/>
       <c r="J15" s="20"/>
       <c r="K15" s="21"/>
-      <c r="L15" s="22"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:14">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="16"/>
       <c r="G16" s="17"/>
       <c r="H16" s="18"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
       <c r="K16" s="21"/>
-      <c r="L16" s="22"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="16"/>
       <c r="G17" s="17"/>
       <c r="H17" s="18"/>
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
       <c r="K17" s="21"/>
-      <c r="L17" s="22"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="25" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="28" t="s">
+      <c r="F18" s="34"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="27" t="s">
+      <c r="I18" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="30">
+      <c r="J18" s="37">
         <f>G18/17</f>
         <v>0</v>
       </c>
-      <c r="K18" s="31" t="s">
+      <c r="K18" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="L18" s="32"/>
+      <c r="L18" s="39"/>
     </row>
     <row r="19" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A19" s="33"/>
-      <c r="B19" s="25" t="s">
+      <c r="A19" s="40"/>
+      <c r="B19" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="25" t="s">
+      <c r="C19" s="41"/>
+      <c r="D19" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="28" t="s">
+      <c r="I19" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="35"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="42"/>
     </row>
     <row r="20" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A20" s="33"/>
-      <c r="B20" s="25" t="s">
+      <c r="A20" s="40"/>
+      <c r="B20" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="25" t="s">
+      <c r="C20" s="41"/>
+      <c r="D20" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="28" t="s">
+      <c r="F20" s="34"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="I20" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="36">
+      <c r="J20" s="44">
         <f>G20/20</f>
         <v>0</v>
       </c>
-      <c r="K20" s="37" t="s">
+      <c r="K20" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="35"/>
+      <c r="L20" s="42"/>
     </row>
     <row r="21" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A21" s="33"/>
-      <c r="B21" s="25" t="s">
+      <c r="A21" s="40"/>
+      <c r="B21" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="I21" s="28" t="s">
+      <c r="C21" s="41"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="I21" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="35"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="42"/>
     </row>
     <row r="22" ht="14.4" customHeight="1" spans="1:12">
-      <c r="A22" s="38"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="41"/>
+      <c r="A22" s="46"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="51"/>
     </row>
     <row r="23" ht="3.75" customHeight="1" spans="1:12">
-      <c r="A23" s="42"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
     </row>
     <row r="24" ht="27" customHeight="1" spans="1:12">
       <c r="A24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
       <c r="G24" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="42"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
     </row>
     <row r="25" ht="6.75" customHeight="1" spans="1:12">
       <c r="A25" s="6"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="42"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
     </row>
     <row r="26" ht="17.25" customHeight="1" spans="1:12">
       <c r="A26" s="5" t="s">
@@ -3141,36 +3159,36 @@
         <v>27</v>
       </c>
       <c r="H26" s="5"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
     </row>
     <row r="27" ht="9.75" customHeight="1" spans="1:12">
-      <c r="A27" s="42"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="42"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="52"/>
     </row>
     <row r="29" ht="19.35" customHeight="1"/>
   </sheetData>
